--- a/data/nzd0021/nzd0021.xlsx
+++ b/data/nzd0021/nzd0021.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E243"/>
+  <dimension ref="A1:E244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5533,6 +5533,27 @@
         <v>364.86</v>
       </c>
       <c r="E243" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>353.84</v>
+      </c>
+      <c r="C244" t="n">
+        <v>348.94</v>
+      </c>
+      <c r="D244" t="n">
+        <v>365.5</v>
+      </c>
+      <c r="E244" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -5549,7 +5570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B259"/>
+  <dimension ref="A1:B260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8142,6 +8163,16 @@
       </c>
       <c r="B259" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -8310,28 +8341,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3021647696662999</v>
+        <v>-0.3103709460305313</v>
       </c>
       <c r="J2" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K2" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09440224231774741</v>
+        <v>0.09930363818168564</v>
       </c>
       <c r="M2" t="n">
-        <v>5.6937396900944</v>
+        <v>5.707340225351003</v>
       </c>
       <c r="N2" t="n">
-        <v>51.87077703041371</v>
+        <v>52.05310391641561</v>
       </c>
       <c r="O2" t="n">
-        <v>7.202136976648924</v>
+        <v>7.214783705449222</v>
       </c>
       <c r="P2" t="n">
-        <v>371.6666458744062</v>
+        <v>371.7431608382744</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8388,28 +8419,28 @@
         <v>0.0956</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1882220516726496</v>
+        <v>-0.1953113490343455</v>
       </c>
       <c r="J3" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K3" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03389770571458561</v>
+        <v>0.0365852205165812</v>
       </c>
       <c r="M3" t="n">
-        <v>6.163155343970057</v>
+        <v>6.169107394204299</v>
       </c>
       <c r="N3" t="n">
-        <v>59.79651664648549</v>
+        <v>59.84582384314903</v>
       </c>
       <c r="O3" t="n">
-        <v>7.732820743201377</v>
+        <v>7.736008262867164</v>
       </c>
       <c r="P3" t="n">
-        <v>362.4188377311024</v>
+        <v>362.4849388368312</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8466,28 +8497,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.003739006441024681</v>
+        <v>-0.006751927629578354</v>
       </c>
       <c r="J4" t="n">
+        <v>243</v>
+      </c>
+      <c r="K4" t="n">
         <v>242</v>
       </c>
-      <c r="K4" t="n">
-        <v>241</v>
-      </c>
       <c r="L4" t="n">
-        <v>2.637456716902964e-05</v>
+        <v>8.672904646567225e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>4.288762424219598</v>
+        <v>4.285846134226846</v>
       </c>
       <c r="N4" t="n">
-        <v>31.07367009882502</v>
+        <v>30.99784668418574</v>
       </c>
       <c r="O4" t="n">
-        <v>5.574376207148655</v>
+        <v>5.567570986003298</v>
       </c>
       <c r="P4" t="n">
-        <v>369.188171414994</v>
+        <v>369.2165192308018</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -8529,7 +8560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E243"/>
+  <dimension ref="A1:E244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15089,6 +15120,33 @@
         </is>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>-34.80758370302159,173.163709740287</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>-34.80831111652472,173.16354792405772</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>-34.80906118542066,173.16362608351085</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0021/nzd0021.xlsx
+++ b/data/nzd0021/nzd0021.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E244"/>
+  <dimension ref="A1:E246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5554,6 +5554,48 @@
         <v>365.5</v>
       </c>
       <c r="E244" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>351.6</v>
+      </c>
+      <c r="C245" t="n">
+        <v>344.18</v>
+      </c>
+      <c r="D245" t="n">
+        <v>362.79</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>352.24</v>
+      </c>
+      <c r="C246" t="n">
+        <v>345.59</v>
+      </c>
+      <c r="D246" t="n">
+        <v>363.13</v>
+      </c>
+      <c r="E246" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -5570,7 +5612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B260"/>
+  <dimension ref="A1:B262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8173,6 +8215,26 @@
       </c>
       <c r="B260" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>0.92</v>
       </c>
     </row>
   </sheetData>
@@ -8341,28 +8403,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3103709460305313</v>
+        <v>-0.3292953451312882</v>
       </c>
       <c r="J2" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K2" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09930363818168564</v>
+        <v>0.1103312070558752</v>
       </c>
       <c r="M2" t="n">
-        <v>5.707340225351003</v>
+        <v>5.749938452400848</v>
       </c>
       <c r="N2" t="n">
-        <v>52.05310391641561</v>
+        <v>52.7042680509059</v>
       </c>
       <c r="O2" t="n">
-        <v>7.214783705449222</v>
+        <v>7.259770523295202</v>
       </c>
       <c r="P2" t="n">
-        <v>371.7431608382744</v>
+        <v>371.9202044646335</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8419,28 +8481,28 @@
         <v>0.0956</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1953113490343455</v>
+        <v>-0.2155495355288356</v>
       </c>
       <c r="J3" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K3" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0365852205165812</v>
+        <v>0.04417805129069097</v>
       </c>
       <c r="M3" t="n">
-        <v>6.169107394204299</v>
+        <v>6.208809164741361</v>
       </c>
       <c r="N3" t="n">
-        <v>59.84582384314903</v>
+        <v>60.59115654455895</v>
       </c>
       <c r="O3" t="n">
-        <v>7.736008262867164</v>
+        <v>7.784032152076387</v>
       </c>
       <c r="P3" t="n">
-        <v>362.4849388368312</v>
+        <v>362.6742706538928</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8497,28 +8559,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.006751927629578354</v>
+        <v>-0.01672439058785059</v>
       </c>
       <c r="J4" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K4" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L4" t="n">
-        <v>8.672904646567225e-05</v>
+        <v>0.0005374575963069672</v>
       </c>
       <c r="M4" t="n">
-        <v>4.285846134226846</v>
+        <v>4.299042581342757</v>
       </c>
       <c r="N4" t="n">
-        <v>30.99784668418574</v>
+        <v>31.03829200076854</v>
       </c>
       <c r="O4" t="n">
-        <v>5.567570986003298</v>
+        <v>5.571202024767056</v>
       </c>
       <c r="P4" t="n">
-        <v>369.2165192308018</v>
+        <v>369.3106590457763</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -8560,7 +8622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E244"/>
+  <dimension ref="A1:E246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15147,6 +15209,60 @@
         </is>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>-34.807581286927835,173.1636854258647</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>-34.80830614605051,173.16349623192878</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>-34.809058448911294,173.16359664051149</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>-34.80758197724083,173.16369237284238</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>-34.80830761839916,173.1635115440924</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>-34.80905879223759,173.16360033446702</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0021/nzd0021.xlsx
+++ b/data/nzd0021/nzd0021.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E246"/>
+  <dimension ref="A1:E247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5598,6 +5598,27 @@
       <c r="E246" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>355.87</v>
+      </c>
+      <c r="C247" t="n">
+        <v>348.53</v>
+      </c>
+      <c r="D247" t="n">
+        <v>364</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B262"/>
+  <dimension ref="A1:B263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8235,6 +8256,16 @@
       </c>
       <c r="B262" t="n">
         <v>0.92</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -8403,28 +8434,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3292953451312882</v>
+        <v>-0.3352587573789392</v>
       </c>
       <c r="J2" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K2" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1103312070558752</v>
+        <v>0.1145250283000383</v>
       </c>
       <c r="M2" t="n">
-        <v>5.749938452400848</v>
+        <v>5.754813120101093</v>
       </c>
       <c r="N2" t="n">
-        <v>52.7042680509059</v>
+        <v>52.70133565853187</v>
       </c>
       <c r="O2" t="n">
-        <v>7.259770523295202</v>
+        <v>7.259568558704565</v>
       </c>
       <c r="P2" t="n">
-        <v>371.9202044646335</v>
+        <v>371.9767144272981</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8481,28 +8512,28 @@
         <v>0.0956</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2155495355288356</v>
+        <v>-0.2224430403333897</v>
       </c>
       <c r="J3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04417805129069097</v>
+        <v>0.04716017143176987</v>
       </c>
       <c r="M3" t="n">
-        <v>6.208809164741361</v>
+        <v>6.215095795212609</v>
       </c>
       <c r="N3" t="n">
-        <v>60.59115654455895</v>
+        <v>60.62721929972628</v>
       </c>
       <c r="O3" t="n">
-        <v>7.784032152076387</v>
+        <v>7.786348264734007</v>
       </c>
       <c r="P3" t="n">
-        <v>362.6742706538928</v>
+        <v>362.7395942778444</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8559,28 +8590,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01672439058785059</v>
+        <v>-0.02075497334830816</v>
       </c>
       <c r="J4" t="n">
+        <v>246</v>
+      </c>
+      <c r="K4" t="n">
         <v>245</v>
       </c>
-      <c r="K4" t="n">
-        <v>244</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0005374575963069672</v>
+        <v>0.0008334021132196945</v>
       </c>
       <c r="M4" t="n">
-        <v>4.299042581342757</v>
+        <v>4.300563252645672</v>
       </c>
       <c r="N4" t="n">
-        <v>31.03829200076854</v>
+        <v>31.00674126458397</v>
       </c>
       <c r="O4" t="n">
-        <v>5.571202024767056</v>
+        <v>5.56836971335273</v>
       </c>
       <c r="P4" t="n">
-        <v>369.3106590457763</v>
+        <v>369.3491943947809</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -8622,7 +8653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E246"/>
+  <dimension ref="A1:E247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15263,6 +15294,33 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>-34.80758589260234,173.16373177523343</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>-34.8083106883965,173.16354347158418</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>-34.809059670748475,173.16360978664753</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0021/nzd0021.xlsx
+++ b/data/nzd0021/nzd0021.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E247"/>
+  <dimension ref="A1:E249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5619,6 +5619,48 @@
       <c r="E247" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>355.08</v>
+      </c>
+      <c r="C248" t="n">
+        <v>347.19</v>
+      </c>
+      <c r="D248" t="n">
+        <v>362.82</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>353.34</v>
+      </c>
+      <c r="C249" t="n">
+        <v>346.69</v>
+      </c>
+      <c r="D249" t="n">
+        <v>362.5</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B263"/>
+  <dimension ref="A1:B265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8266,6 +8308,26 @@
       </c>
       <c r="B263" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>-0.36</v>
       </c>
     </row>
   </sheetData>
@@ -8434,28 +8496,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3352587573789392</v>
+        <v>-0.3493820557658821</v>
       </c>
       <c r="J2" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K2" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1145250283000383</v>
+        <v>0.1240539136677853</v>
       </c>
       <c r="M2" t="n">
-        <v>5.754813120101093</v>
+        <v>5.775279657402146</v>
       </c>
       <c r="N2" t="n">
-        <v>52.70133565853187</v>
+        <v>52.89096819433845</v>
       </c>
       <c r="O2" t="n">
-        <v>7.259568558704565</v>
+        <v>7.272617698898963</v>
       </c>
       <c r="P2" t="n">
-        <v>371.9767144272981</v>
+        <v>372.1108099619759</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8512,28 +8574,28 @@
         <v>0.0956</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2224430403333897</v>
+        <v>-0.2382421656709696</v>
       </c>
       <c r="J3" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K3" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04716017143176987</v>
+        <v>0.0540973048682134</v>
       </c>
       <c r="M3" t="n">
-        <v>6.215095795212609</v>
+        <v>6.236899244389868</v>
       </c>
       <c r="N3" t="n">
-        <v>60.62721929972628</v>
+        <v>60.90059125950754</v>
       </c>
       <c r="O3" t="n">
-        <v>7.786348264734007</v>
+        <v>7.803883088534037</v>
       </c>
       <c r="P3" t="n">
-        <v>362.7395942778444</v>
+        <v>362.8895906852266</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8590,28 +8652,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02075497334830816</v>
+        <v>-0.03068171515215267</v>
       </c>
       <c r="J4" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K4" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008334021132196945</v>
+        <v>0.001838427969743539</v>
       </c>
       <c r="M4" t="n">
-        <v>4.300563252645672</v>
+        <v>4.31281095942072</v>
       </c>
       <c r="N4" t="n">
-        <v>31.00674126458397</v>
+        <v>31.05231314307495</v>
       </c>
       <c r="O4" t="n">
-        <v>5.56836971335273</v>
+        <v>5.57246024149791</v>
       </c>
       <c r="P4" t="n">
-        <v>369.3491943947809</v>
+        <v>369.4442786932797</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -8653,7 +8715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E247"/>
+  <dimension ref="A1:E249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15321,6 +15383,60 @@
         </is>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>-34.80758504049996,173.1637232000571</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>-34.80830928914705,173.16352891959784</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>-34.80905847920481,173.16359696644875</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>-34.80758316371536,173.16370431296048</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>-34.808308767038596,173.1635234897523</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>-34.80905815607409,173.16359348978474</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0021/nzd0021.xlsx
+++ b/data/nzd0021/nzd0021.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E249"/>
+  <dimension ref="A1:E250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5661,6 +5661,27 @@
       <c r="E249" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>352.85</v>
+      </c>
+      <c r="C250" t="n">
+        <v>345.86</v>
+      </c>
+      <c r="D250" t="n">
+        <v>362.46</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B265"/>
+  <dimension ref="A1:B266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8328,6 +8349,16 @@
       </c>
       <c r="B265" t="n">
         <v>-0.36</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -8496,28 +8527,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3493820557658821</v>
+        <v>-0.3572559953605054</v>
       </c>
       <c r="J2" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K2" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1240539136677853</v>
+        <v>0.129260088353565</v>
       </c>
       <c r="M2" t="n">
-        <v>5.775279657402146</v>
+        <v>5.78987211359448</v>
       </c>
       <c r="N2" t="n">
-        <v>52.89096819433845</v>
+        <v>53.06603981430825</v>
       </c>
       <c r="O2" t="n">
-        <v>7.272617698898963</v>
+        <v>7.284644110339794</v>
       </c>
       <c r="P2" t="n">
-        <v>372.1108099619759</v>
+        <v>372.1858457017028</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8574,28 +8605,28 @@
         <v>0.0956</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2382421656709696</v>
+        <v>-0.2467158198726962</v>
       </c>
       <c r="J3" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K3" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0540973048682134</v>
+        <v>0.0579214758383455</v>
       </c>
       <c r="M3" t="n">
-        <v>6.236899244389868</v>
+        <v>6.24998140121351</v>
       </c>
       <c r="N3" t="n">
-        <v>60.90059125950754</v>
+        <v>61.10476874997984</v>
       </c>
       <c r="O3" t="n">
-        <v>7.803883088534037</v>
+        <v>7.816953930398966</v>
       </c>
       <c r="P3" t="n">
-        <v>362.8895906852266</v>
+        <v>362.9703414839311</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8652,28 +8683,28 @@
         <v>0.075</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03068171515215267</v>
+        <v>-0.03562940755608131</v>
       </c>
       <c r="J4" t="n">
+        <v>249</v>
+      </c>
+      <c r="K4" t="n">
         <v>248</v>
       </c>
-      <c r="K4" t="n">
-        <v>247</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.001838427969743539</v>
+        <v>0.002489974649132365</v>
       </c>
       <c r="M4" t="n">
-        <v>4.31281095942072</v>
+        <v>4.318748511788064</v>
       </c>
       <c r="N4" t="n">
-        <v>31.05231314307495</v>
+        <v>31.07791649808957</v>
       </c>
       <c r="O4" t="n">
-        <v>5.57246024149791</v>
+        <v>5.574757079738055</v>
       </c>
       <c r="P4" t="n">
-        <v>369.4442786932797</v>
+        <v>369.4918469864751</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -8715,7 +8746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E249"/>
+  <dimension ref="A1:E250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15437,6 +15468,33 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>-34.80758263519503,173.16369899418055</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>-34.80830790033802,173.1635144762089</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>-34.80905811568274,173.16359305520174</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
